--- a/data/mobilite.xlsx
+++ b/data/mobilite.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="convention" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
   <si>
     <t xml:space="preserve">cle</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t xml:space="preserve">responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">progression</t>
   </si>
   <si>
     <t xml:space="preserve">Analyse comparative bus / transport à la demande</t>
@@ -341,7 +344,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -371,6 +374,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -804,7 +811,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -826,25 +833,31 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -852,19 +865,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -872,19 +885,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -892,19 +905,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +944,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>27</v>
@@ -936,10 +952,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -963,22 +979,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">SUMIF(A:A,"poste",C:C)</f>
@@ -991,10 +1007,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>80000</v>
@@ -1006,10 +1022,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>20000</v>
@@ -1021,10 +1037,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>28000</v>
@@ -1036,10 +1052,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>22000</v>
@@ -1070,18 +1086,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1250</v>
@@ -1092,7 +1108,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1380</v>
@@ -1103,7 +1119,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1420</v>
@@ -1114,7 +1130,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1310</v>
@@ -1125,7 +1141,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1490</v>
@@ -1136,7 +1152,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1200</v>
@@ -1147,7 +1163,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>980</v>
@@ -1158,7 +1174,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>870</v>
@@ -1169,7 +1185,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1350</v>
@@ -1180,7 +1196,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1480</v>
@@ -1191,7 +1207,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1390</v>
@@ -1202,7 +1218,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1100</v>
